--- a/testakten/statusfeststellung-gmbh-geschaeftsfuehrer-minderheit-erlangen/xlsx/buergschaft_und_darlehen_zahlungsfluesse.xlsx
+++ b/testakten/statusfeststellung-gmbh-geschaeftsfuehrer-minderheit-erlangen/xlsx/buergschaft_und_darlehen_zahlungsfluesse.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Uebernahme persoenliche Buergschaft ggue. Sparkasse Erlangen</t>
+          <t>Übernahme persönliche Bürgschaft gegenüber. Sparkasse Erlangen</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -458,7 +458,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Buergschaftsurkunde Nr. 2021-0417</t>
+          <t>Bürgschaftsurkunde Nr. 2021-0417</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stand Inanspruchnahme Buergschaft</t>
+          <t>Stand Inanspruchnahme Bürgschaft</t>
         </is>
       </c>
       <c r="C5" t="n">
